--- a/data-raw/biomes_information.xlsx
+++ b/data-raw/biomes_information.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcgro\Documents\biomer\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcgro\Documents\biomes\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA04ABED-7B6C-41FF-B3A1-79B85B2CD279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A604B2A-CDE2-4488-92EE-C85C1D809141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F78F481E-0242-4623-B044-3E9517C148F9}"/>
+    <workbookView xWindow="29220" yWindow="-12750" windowWidth="21600" windowHeight="11175" xr2:uid="{F78F481E-0242-4623-B044-3E9517C148F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>Layer in RasterStack</t>
   </si>
   <si>
-    <t xml:space="preserve">Background and specifications </t>
-  </si>
-  <si>
     <t>Number of classes (zonal/azonal)</t>
   </si>
   <si>
@@ -711,6 +708,9 @@
   </si>
   <si>
     <t>For this classification, biomes are defined as consistent terrestrial ecological regions to form habitats which correspond to relatively uniform landscapes. Those fundamental global ecological units are characterized by similar vegetation and fauna. Important shaping factors are climate and soil. The concept includes ecotones which mark small-scale transition zones between distinct areas of certain exclusive classes. Zonobiomes are zonally connected and azonal relief units, like mountain systems, are defined as orobiomes.  The first version consisted of two volumes with the original title “Die Vegetation der Erde in öko-physiologischer Betrachtung“ (Walter, 1964, 1968). There have been several later English and German editions of this fundamental book series over the past decades. Those include among others Walter (1973, 1979, 1984, 1990) and Walter &amp; Breckle (1985, 1991, 1999). The map consulted in this inventory was taken from the last edition by Breckle &amp; Rafiqpoor (2019).</t>
+  </si>
+  <si>
+    <t>Background and specifications</t>
   </si>
 </sst>
 </file>
@@ -1102,1107 +1102,1107 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
       </c>
       <c r="H2">
         <v>-1.3</v>
       </c>
       <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
         <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
       </c>
       <c r="H3">
         <v>-4.6500000000000004</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
         <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
       </c>
       <c r="H4">
         <v>5.13</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
         <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
         <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>41</v>
       </c>
       <c r="H5">
         <v>-13.57</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s">
         <v>42</v>
-      </c>
-      <c r="K5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>46</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" t="s">
         <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
       </c>
       <c r="H6">
         <v>4.49</v>
       </c>
       <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>51</v>
-      </c>
-      <c r="K6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>54</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>55</v>
-      </c>
-      <c r="D7" t="s">
-        <v>56</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H7">
         <v>-6.91</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" t="s">
         <v>58</v>
-      </c>
-      <c r="K7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s">
         <v>60</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>61</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" t="s">
         <v>64</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
       </c>
       <c r="H8">
         <v>-3.87</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
         <v>67</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
         <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" t="s">
         <v>64</v>
-      </c>
-      <c r="G9" t="s">
-        <v>65</v>
       </c>
       <c r="H9">
         <v>-3.87</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
         <v>70</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>71</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>73</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
         <v>74</v>
-      </c>
-      <c r="G10" t="s">
-        <v>75</v>
       </c>
       <c r="H10">
         <v>0.98</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
         <v>77</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>78</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>79</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H11">
         <v>4.87</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" t="s">
         <v>82</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
         <v>84</v>
       </c>
-      <c r="B12" t="s">
-        <v>85</v>
-      </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12">
         <v>4.5599999999999996</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" t="s">
         <v>58</v>
-      </c>
-      <c r="K12" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
       </c>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" t="s">
         <v>91</v>
-      </c>
-      <c r="G13" t="s">
-        <v>92</v>
       </c>
       <c r="H13">
         <v>-3.62</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" t="s">
         <v>93</v>
-      </c>
-      <c r="K13" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
         <v>95</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>96</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>97</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
       </c>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" t="s">
         <v>99</v>
-      </c>
-      <c r="G14" t="s">
-        <v>100</v>
       </c>
       <c r="H14">
         <v>5.0999999999999996</v>
       </c>
       <c r="I14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
+        <v>100</v>
+      </c>
+      <c r="K14" t="s">
         <v>101</v>
-      </c>
-      <c r="K14" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
         <v>103</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>104</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>105</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H15">
         <v>3.45</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" t="s">
         <v>108</v>
-      </c>
-      <c r="K15" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" t="s">
         <v>110</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>111</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
       </c>
       <c r="E16">
         <v>15</v>
       </c>
       <c r="F16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" t="s">
         <v>114</v>
-      </c>
-      <c r="G16" t="s">
-        <v>115</v>
       </c>
       <c r="H16">
         <v>4.5999999999999996</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
+        <v>115</v>
+      </c>
+      <c r="K16" t="s">
         <v>116</v>
-      </c>
-      <c r="K16" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
         <v>118</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>119</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>120</v>
-      </c>
-      <c r="D17" t="s">
-        <v>121</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H17">
         <v>-4.79</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" t="s">
+        <v>122</v>
+      </c>
+      <c r="K17" t="s">
         <v>123</v>
-      </c>
-      <c r="K17" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" t="s">
         <v>125</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>126</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>127</v>
-      </c>
-      <c r="D18" t="s">
-        <v>128</v>
       </c>
       <c r="E18">
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H18">
         <v>-5.58</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" t="s">
         <v>131</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>132</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>133</v>
-      </c>
-      <c r="D19" t="s">
-        <v>134</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
       <c r="F19" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" t="s">
         <v>135</v>
-      </c>
-      <c r="G19" t="s">
-        <v>136</v>
       </c>
       <c r="H19">
         <v>3.47</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" t="s">
         <v>137</v>
-      </c>
-      <c r="K19" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s">
         <v>139</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>140</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>141</v>
-      </c>
-      <c r="D20" t="s">
-        <v>142</v>
       </c>
       <c r="E20">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H20">
         <v>5.2</v>
       </c>
       <c r="I20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s">
         <v>145</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
         <v>146</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>147</v>
       </c>
       <c r="E21">
         <v>20</v>
       </c>
       <c r="F21" t="s">
+        <v>147</v>
+      </c>
+      <c r="G21" t="s">
         <v>148</v>
-      </c>
-      <c r="G21" t="s">
-        <v>149</v>
       </c>
       <c r="H21">
         <v>5.18</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" t="s">
         <v>151</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>152</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>153</v>
-      </c>
-      <c r="D22" t="s">
-        <v>154</v>
       </c>
       <c r="E22">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H22">
         <v>-5.89</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" t="s">
         <v>156</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>157</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>158</v>
-      </c>
-      <c r="D23" t="s">
-        <v>159</v>
       </c>
       <c r="E23">
         <v>22</v>
       </c>
       <c r="F23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" t="s">
         <v>160</v>
-      </c>
-      <c r="G23" t="s">
-        <v>161</v>
       </c>
       <c r="H23">
         <v>-5.55</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
+        <v>161</v>
+      </c>
+      <c r="K23" t="s">
         <v>162</v>
-      </c>
-      <c r="K23" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s">
         <v>164</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>165</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>166</v>
-      </c>
-      <c r="D24" t="s">
-        <v>167</v>
       </c>
       <c r="E24">
         <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H24">
         <v>5.14</v>
       </c>
       <c r="I24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J24" t="s">
+        <v>168</v>
+      </c>
+      <c r="K24" t="s">
         <v>169</v>
-      </c>
-      <c r="K24" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" t="s">
         <v>171</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>172</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>173</v>
-      </c>
-      <c r="D25" t="s">
-        <v>174</v>
       </c>
       <c r="E25">
         <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H25">
         <v>3.89</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J25" t="s">
+        <v>175</v>
+      </c>
+      <c r="K25" t="s">
         <v>176</v>
-      </c>
-      <c r="K25" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" t="s">
         <v>178</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
         <v>179</v>
-      </c>
-      <c r="C26" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" t="s">
-        <v>180</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" t="s">
         <v>181</v>
-      </c>
-      <c r="G26" t="s">
-        <v>182</v>
       </c>
       <c r="H26">
         <v>-4.25</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J26" t="s">
+        <v>182</v>
+      </c>
+      <c r="K26" t="s">
         <v>183</v>
-      </c>
-      <c r="K26" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" t="s">
         <v>185</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>186</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>187</v>
-      </c>
-      <c r="D27" t="s">
-        <v>188</v>
       </c>
       <c r="E27">
         <v>26</v>
       </c>
       <c r="F27" t="s">
+        <v>188</v>
+      </c>
+      <c r="G27" t="s">
         <v>189</v>
-      </c>
-      <c r="G27" t="s">
-        <v>190</v>
       </c>
       <c r="H27">
         <v>0.56000000000000005</v>
       </c>
       <c r="I27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J27" t="s">
+        <v>190</v>
+      </c>
+      <c r="K27" t="s">
         <v>191</v>
-      </c>
-      <c r="K27" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>192</v>
+      </c>
+      <c r="B28" t="s">
         <v>193</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>194</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>195</v>
-      </c>
-      <c r="D28" t="s">
-        <v>196</v>
       </c>
       <c r="E28">
         <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H28">
         <v>4.87</v>
       </c>
       <c r="I28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" t="s">
         <v>82</v>
-      </c>
-      <c r="K28" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" t="s">
         <v>198</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>199</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>200</v>
-      </c>
-      <c r="D29" t="s">
-        <v>201</v>
       </c>
       <c r="E29">
         <v>28</v>
       </c>
       <c r="F29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H29">
         <v>4.8600000000000003</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J29" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29" t="s">
         <v>82</v>
-      </c>
-      <c r="K29" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" t="s">
         <v>203</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>204</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>205</v>
-      </c>
-      <c r="D30" t="s">
-        <v>206</v>
       </c>
       <c r="E30">
         <v>29</v>
       </c>
       <c r="F30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H30">
         <v>4.87</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J30" t="s">
+        <v>81</v>
+      </c>
+      <c r="K30" t="s">
         <v>82</v>
-      </c>
-      <c r="K30" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" t="s">
         <v>208</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>209</v>
       </c>
-      <c r="C31" t="s">
-        <v>210</v>
-      </c>
       <c r="D31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E31">
         <v>30</v>
       </c>
       <c r="F31" t="s">
+        <v>210</v>
+      </c>
+      <c r="G31" t="s">
         <v>211</v>
-      </c>
-      <c r="G31" t="s">
-        <v>212</v>
       </c>
       <c r="H31">
         <v>-3.69</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J31" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" t="s">
         <v>82</v>
-      </c>
-      <c r="K31" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" t="s">
         <v>213</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>214</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>215</v>
-      </c>
-      <c r="D32" t="s">
-        <v>216</v>
       </c>
       <c r="E32">
         <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H32">
         <v>-3.69</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J32" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" t="s">
         <v>82</v>
-      </c>
-      <c r="K32" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
